--- a/branches/chore/point-skills-at-catalog/StructureDefinition-preview-model.xlsx
+++ b/branches/chore/point-skills-at-catalog/StructureDefinition-preview-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T12:35:04+00:00</t>
+    <t>2026-08-06T13:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
